--- a/data_u1/soe_tables_2025.08.15.xlsx
+++ b/data_u1/soe_tables_2025.08.15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41C3DA8-18AA-7F48-B9BA-5A9B9975B7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1697C41-836B-5A41-8A4B-6AFFDCE438BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="8" xr2:uid="{5B3852FF-2BEC-B94D-907F-9BD79E8D9C2A}"/>
+    <workbookView xWindow="-22300" yWindow="-21100" windowWidth="38400" windowHeight="19840" activeTab="8" xr2:uid="{5B3852FF-2BEC-B94D-907F-9BD79E8D9C2A}"/>
   </bookViews>
   <sheets>
     <sheet name="sch_ac_ta1_pl_eff" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="255">
   <si>
     <t>Outcome</t>
   </si>
@@ -144,12 +144,6 @@
   </si>
   <si>
     <t>N=1 n=214; 26.5% vs. 48.6%, OR=0.38, 95%CI: 0.21, 0.68</t>
-  </si>
-  <si>
-    <t>N=1 n=71; 15.3% vs. 1.4%, OR=13.16, 95%CI: 0.7, 247.71</t>
-  </si>
-  <si>
-    <t>N=1 n=214; 1.4% vs. 8.1%, OR=0.16, 95%CI: 0.03, 0.84</t>
   </si>
   <si>
     <t>N=1 n=214; 1.4% vs. 10.8%, OR=0.12, 95%CI: 0.02, 0.58</t>
@@ -331,9 +325,6 @@
     <t>N=1 n=303; 3.5% vs. 11.8%, OR=0.27, 95%CI: 0.1, 0.71</t>
   </si>
   <si>
-    <t>N=2 n=133; Random-effects: 22.8% vs. 2.3%, OR=12.62, 95%CI: 2.25, 70.79; Fixed-effecs: OR=12.6, 95%CI: 2.25, 70.72</t>
-  </si>
-  <si>
     <t>N=1 n=303; MD=-2.6, 95%CI: -4.12, -1.08</t>
   </si>
   <si>
@@ -523,24 +514,15 @@
     <t>Serious adverse events (6.1.12)</t>
   </si>
   <si>
-    <t>N=4 n=177; Random-effects: 0% vs. 0%, OR=3.02, 95%CI: 0.36, 25.76; Fixed-effecs: OR=3.02, 95%CI: 0.36, 25.76 (two studies reported 0 events in both arms)</t>
-  </si>
-  <si>
     <t>Death due to any cause (6.1.13)</t>
   </si>
   <si>
-    <t>N=7 n=1451; 0% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11 (six studies reported 0 events in both harms)</t>
-  </si>
-  <si>
     <t>N=4 n=177; Random-effects: 48.9% vs. 10.1%, OR=8.49, 95%CI: 1.73, 41.66; Fixed-effecs: OR=9.3, 95%CI: 3.92, 22.08</t>
   </si>
   <si>
     <t>Any adverse event (6.1.14)</t>
   </si>
   <si>
-    <t>N=1 n=69; 0% vs. 0%, OR=12.44, 95%CI: 0.66, 234.38</t>
-  </si>
-  <si>
     <t>N=3 n=490; Random-effects: 0.5% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.39, 95%CI: 0.18, 10.67 (one study had 0 events in both arms)</t>
   </si>
   <si>
@@ -568,18 +550,12 @@
     <t>Nausea/vomitting (6.1.18)</t>
   </si>
   <si>
-    <t>N=3 n=161; Random-effects: 10.8% vs. 0.8%, OR=15.14, 95%CI: 3.71, 61.75; Fixed-effecs: OR=15.14, 95%CI: 3.71, 61.75</t>
-  </si>
-  <si>
     <t>N=4 n=524; Random-effects: 5% vs. 4.4%, OR=1.15, 95%CI: 0.34, 3.88, 95%PI: 0.64, 2.41; Fixed-effecs: OR=1.14, 95%CI: 0.5, 2.64</t>
   </si>
   <si>
     <t>N=7 n=1451; Random-effects: 49.7% vs. 46.5%, OR=1.14, 95%CI: 0.81, 1.61, 95%PI: 0.50, 2.59; Fixed-effecs: OR=1.22, 95%CI: 0.98, 1.52</t>
   </si>
   <si>
-    <t>N=7 n=1451; Random-effects: 5.6% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74, 95%PI: 0.94, 4.51; Fixed-effecs: OR=2.1, 95%CI: 1.18, 3.73 (one study reported 0 events in both arms)</t>
-  </si>
-  <si>
     <t>N=7 n=1451; Random-effects: 9.3% vs. 6.1%, OR=1.57, 95%CI: 1.02, 2.42, 95%PI: 0.89, 2.76; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47 (one study reported 0 events in both arms)</t>
   </si>
   <si>
@@ -589,9 +565,6 @@
     <t>QTc prolongation (any cut-off) (6.1.19)</t>
   </si>
   <si>
-    <t>N=2 n=92; 8.1% vs. 1.6%, OR=5.32, 95%CI: 0.6, 46.78 (one study had 0 events in both arms)</t>
-  </si>
-  <si>
     <t>QTc interval (msec) (6.1.20)</t>
   </si>
   <si>
@@ -652,9 +625,6 @@
     <t>Insomnia (6.1.31)</t>
   </si>
   <si>
-    <t>N=3 n=161; Random-effects: 5.6% vs. 0.6%, OR=9.55, 95%CI: 3.5, 26.09; Fixed-effecs: OR=9.55, 95%CI: 3.5, 26.09</t>
-  </si>
-  <si>
     <t>Low risk: 60% studies and 91.3% participants with schizophrenia.</t>
   </si>
   <si>
@@ -670,9 +640,6 @@
     <t>N=7 n=1451; Random-effects: 8.8% vs. 5.2%, OR=1.76, 95%CI: 1.01, 3.08, 95%PI: 0.60, 5.23; Fixed-effecs: OR=1.98, 95%CI: 1.27, 3.06</t>
   </si>
   <si>
-    <t>N=1 n=104; 0% vs. 0%, OR=1.69, 95%CI: 0.07, 42.58</t>
-  </si>
-  <si>
     <t>Worsening of psychosis (6.3.32)</t>
   </si>
   <si>
@@ -727,15 +694,6 @@
     <t>Serious adverse events (6.2.12)</t>
   </si>
   <si>
-    <t>N=2 n=133; 0% vs. 0%, OR=3.17, 95%CI: 0.13, 80.58 (one study reported 0 events in both arms)</t>
-  </si>
-  <si>
-    <t>N=1 n=214; 0% vs. 0%, OR=3.79, 95%CI: 0.19, 74.42</t>
-  </si>
-  <si>
-    <t>N=1 n=303; 0% vs. 0%, OR=18.23, 95%CI: 1.08, 307.1</t>
-  </si>
-  <si>
     <t>Death due to any cause (6.2.13)</t>
   </si>
   <si>
@@ -745,9 +703,6 @@
     <t>Any adverse event (6.2.14)</t>
   </si>
   <si>
-    <t>N=2 n=133; Random-effects: 87.2% vs. 35.8%, OR=12.17, 95%CI: 1.22, 121.04; Fixed-effecs: OR=9.49, 95%CI: 3.94, 22.84</t>
-  </si>
-  <si>
     <t>N=1 n=303; 76% vs. 75.5%, OR=1.03, 95%CI: 0.59, 1.8</t>
   </si>
   <si>
@@ -799,12 +754,6 @@
     <t>Agitation (6.2.28)</t>
   </si>
   <si>
-    <t>N=1 n=214; 0% vs. 0%, OR=9.56, 95%CI: 0.54, 167.96</t>
-  </si>
-  <si>
-    <t>Headache (6.2.29))</t>
-  </si>
-  <si>
     <t>Sedation (6.2.30)</t>
   </si>
   <si>
@@ -817,13 +766,61 @@
     <t>Worsening of psychosis (6.2.32)</t>
   </si>
   <si>
-    <t>N=2 n=133; Random-effects: 43.1% vs. 8.7%, OR=7.96, 95%CI: 2.84, 22.36; Fixed-effecs: OR=7.81, 95%CI: 2.76, 22.09</t>
-  </si>
-  <si>
     <t>N=1 n=303; 10% vs. 7.8%, OR=1.3, 95%CI: 0.55, 3.06</t>
   </si>
   <si>
     <t>N=1 n=214; 2.1% vs. 1.4%, OR=1.6, 95%CI: 0.16, 15.64</t>
+  </si>
+  <si>
+    <t>N=1 n=71; 15.3% vs. 0%, OR=13.16, 95%CI: 0.7, 247.71</t>
+  </si>
+  <si>
+    <t>N=1 n=69; 15.3% vs. 0%, OR=12.44, 95%CI: 0.66, 234.38</t>
+  </si>
+  <si>
+    <t>N=3 n=161; Random-effects: 10.9% vs. 0.8%, OR=15.34, 95%CI: 3.74, 62.92; Fixed-effecs: OR=15.34, 95%CI: 3.74, 62.92</t>
+  </si>
+  <si>
+    <t>N=2 n=92; 5.5% vs. 1.1%, OR=5.32, 95%CI: 0.6, 46.78 (one study had 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=3 n=161; Random-effects: 5.6% vs. 0.6%, OR=9.6, 95%CI: 3.51, 26.27; Fixed-effecs: OR=9.6, 95%CI: 3.51, 26.27</t>
+  </si>
+  <si>
+    <t>N=1 n=104; 2.2% vs. 0%, OR=1.69, 95%CI: 0.07, 42.58</t>
+  </si>
+  <si>
+    <t>N=4 n=177; Random-effects: 4.6% vs. 0%, OR=3.02, 95%CI: 0.35, 26.43; Fixed-effecs: OR=3.02, 95%CI: 0.35, 26.43 (two studies reported 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74; Fixed-effecs: OR=2.1, 95%CI: 1.18, 3.73 (one study reported 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; 3.2% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11 (six studies reported 0 events in both harms)</t>
+  </si>
+  <si>
+    <t>N=2 n=102; 4.5% vs. 0%, OR=3.17, 95%CI: 0.13, 80.58 (one study reported 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=1 n=214; 2.5% vs. 0%, OR=3.79, 95%CI: 0.19, 74.42</t>
+  </si>
+  <si>
+    <t>N=1 n=303; 8.2% vs. 0%, OR=18.23, 95%CI: 1.08, 307.1</t>
+  </si>
+  <si>
+    <t>N=2 n=102; Random-effects: 87% vs. 35.8%, OR=12.02, 95%CI: 1.21, 119.07; Fixed-effecs: OR=6.69, 95%CI: 2.8, 15.96</t>
+  </si>
+  <si>
+    <t>N=2 n=102; Random-effects: 22.7% vs. 1.5%, OR=12.5, 95%CI: 2.33, 67.21; Fixed-effecs: OR=12.5, 95%CI: 2.33, 67.21</t>
+  </si>
+  <si>
+    <t>N=2 n=102; Random-effects: 30.2% vs. 0%, OR=29.38, 95%CI: 4.04, 213.55; Fixed-effecs: OR=29.38, 95%CI: 4.04, 213.55</t>
+  </si>
+  <si>
+    <t>N=1 n=214; 6% vs. 0%, OR=9.56, 95%CI: 0.54, 167.96</t>
+  </si>
+  <si>
+    <t>N=2 n=102; Random-effects: 42.4% vs. 8.7%, OR=7.78, 95%CI: 2.83, 21.4; Fixed-effecs: OR=7.78, 95%CI: 2.83, 21.4</t>
   </si>
 </sst>
 </file>
@@ -969,7 +966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1012,9 +1009,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1374,131 +1368,131 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="225" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="225" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="225" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="225" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="175" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1532,62 +1526,62 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="333" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="D3" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1611,131 +1605,131 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="G1" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="42" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="126" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="D5" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1759,131 +1753,131 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="G1" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="140" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="140" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="42" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="140" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="140" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1907,62 +1901,62 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1996,44 +1990,44 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>7</v>
@@ -2042,85 +2036,85 @@
         <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2153,21 +2147,21 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="92" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
@@ -2176,21 +2170,21 @@
         <v>10</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>
@@ -2199,21 +2193,21 @@
         <v>11</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>9</v>
@@ -2222,21 +2216,21 @@
         <v>12</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="91" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>9</v>
@@ -2245,16 +2239,16 @@
         <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2286,821 +2280,821 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="100" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>148</v>
+      <c r="C2" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>175</v>
+        <v>80</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>151</v>
+      <c r="C4" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="113" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>174</v>
+        <v>80</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="113" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>155</v>
+      <c r="C6" s="4" t="s">
+        <v>244</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="113" thickBot="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>173</v>
+        <v>80</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>245</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>157</v>
+        <v>80</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>246</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>158</v>
+      <c r="C10" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>172</v>
+        <v>80</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="104" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="16" t="s">
-        <v>160</v>
+      <c r="C12" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="104" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>161</v>
+        <v>74</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="16" t="s">
-        <v>166</v>
+      <c r="C15" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>168</v>
+        <v>81</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="16" t="s">
-        <v>170</v>
+      <c r="C17" s="4" t="s">
+        <v>240</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>171</v>
+        <v>80</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="139" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>177</v>
+      <c r="C19" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>181</v>
+      <c r="C22" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="84" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>186</v>
+      <c r="C27" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="98" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="16" t="s">
-        <v>188</v>
+      <c r="C29" s="4" t="s">
+        <v>179</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>192</v>
+      <c r="C30" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>194</v>
+        <v>80</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="16" t="s">
-        <v>198</v>
+      <c r="C33" s="4" t="s">
+        <v>242</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>200</v>
+        <v>80</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>201</v>
+        <v>80</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>203</v>
+        <v>80</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3133,292 +3127,292 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3453,21 +3447,21 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>14</v>
@@ -3476,21 +3470,21 @@
         <v>27</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>7</v>
@@ -3499,44 +3493,44 @@
         <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>14</v>
@@ -3545,21 +3539,21 @@
         <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -3568,136 +3562,136 @@
         <v>30</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>89</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>7</v>
@@ -3706,67 +3700,67 @@
         <v>31</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>7</v>
@@ -3775,637 +3769,637 @@
         <v>32</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>33</v>
+        <v>238</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>91</v>
+        <v>251</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:7" customFormat="1" ht="139" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>247</v>
+      <c r="C33" s="4" t="s">
+        <v>253</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data_u1/soe_tables_2025.08.15.xlsx
+++ b/data_u1/soe_tables_2025.08.15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1697C41-836B-5A41-8A4B-6AFFDCE438BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F09FFE-FF05-4F4E-9CFF-7B34E80698C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22300" yWindow="-21100" windowWidth="38400" windowHeight="19840" activeTab="8" xr2:uid="{5B3852FF-2BEC-B94D-907F-9BD79E8D9C2A}"/>
+    <workbookView xWindow="-21720" yWindow="-21100" windowWidth="38400" windowHeight="19840" activeTab="6" xr2:uid="{5B3852FF-2BEC-B94D-907F-9BD79E8D9C2A}"/>
   </bookViews>
   <sheets>
     <sheet name="sch_ac_ta1_pl_eff" sheetId="1" r:id="rId1"/>
@@ -523,9 +523,6 @@
     <t>Any adverse event (6.1.14)</t>
   </si>
   <si>
-    <t>N=3 n=490; Random-effects: 0.5% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.39, 95%CI: 0.18, 10.67 (one study had 0 events in both arms)</t>
-  </si>
-  <si>
     <t>Low risk: All studies had an overall low risk of bias.</t>
   </si>
   <si>
@@ -544,24 +541,12 @@
     <t>Low risk: 50% studies and 87.3% participants with schizophrenia.</t>
   </si>
   <si>
-    <t>N=4 n=529; Random-effects: 0.8% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=2.24, 95%CI: 0.34, 14.7 (two studies had 0 events in both arms)</t>
-  </si>
-  <si>
     <t>Nausea/vomitting (6.1.18)</t>
   </si>
   <si>
-    <t>N=4 n=524; Random-effects: 5% vs. 4.4%, OR=1.15, 95%CI: 0.34, 3.88, 95%PI: 0.64, 2.41; Fixed-effecs: OR=1.14, 95%CI: 0.5, 2.64</t>
-  </si>
-  <si>
     <t>N=7 n=1451; Random-effects: 49.7% vs. 46.5%, OR=1.14, 95%CI: 0.81, 1.61, 95%PI: 0.50, 2.59; Fixed-effecs: OR=1.22, 95%CI: 0.98, 1.52</t>
   </si>
   <si>
-    <t>N=7 n=1451; Random-effects: 9.3% vs. 6.1%, OR=1.57, 95%CI: 1.02, 2.42, 95%PI: 0.89, 2.76; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47 (one study reported 0 events in both arms)</t>
-  </si>
-  <si>
-    <t>N=7 n=1451; Random-effects: 23% vs. 19.5%, OR=1.23, 95%CI: 0.94, 1.61, 95%PI: 0.88, 1.72; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
-  </si>
-  <si>
     <t>QTc prolongation (any cut-off) (6.1.19)</t>
   </si>
   <si>
@@ -607,9 +592,6 @@
     <t>Agitation (6.1.28)</t>
   </si>
   <si>
-    <t>N=5 n=1385; Random-effects: 5.3% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.21, 95%CI: 0.72, 2.01</t>
-  </si>
-  <si>
     <t>Headache (6.1.29)</t>
   </si>
   <si>
@@ -628,18 +610,12 @@
     <t>Low risk: 60% studies and 91.3% participants with schizophrenia.</t>
   </si>
   <si>
-    <t>N=5 n=774; Random-effects: 1.6% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.19, 95%CI: 0.48, 2.98 (one study had 0 events in both arms)</t>
-  </si>
-  <si>
     <t>N=4 n=524; Random-effects: 7.6% vs. 6.7%, OR=1.13, 95%CI: 0.27, 4.66, 95%PI: 0.21, 6.29; Fixed-effecs: OR=0.81, 95%CI: 0.38, 1.69</t>
   </si>
   <si>
     <t>Worsening of psychosis (6.1.32)</t>
   </si>
   <si>
-    <t>N=7 n=1451; Random-effects: 8.8% vs. 5.2%, OR=1.76, 95%CI: 1.01, 3.08, 95%PI: 0.60, 5.23; Fixed-effecs: OR=1.98, 95%CI: 1.27, 3.06</t>
-  </si>
-  <si>
     <t>Worsening of psychosis (6.3.32)</t>
   </si>
   <si>
@@ -793,9 +769,6 @@
     <t>N=4 n=177; Random-effects: 4.6% vs. 0%, OR=3.02, 95%CI: 0.35, 26.43; Fixed-effecs: OR=3.02, 95%CI: 0.35, 26.43 (two studies reported 0 events in both arms)</t>
   </si>
   <si>
-    <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74; Fixed-effecs: OR=2.1, 95%CI: 1.18, 3.73 (one study reported 0 events in both arms)</t>
-  </si>
-  <si>
     <t>N=7 n=1451; 3.2% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11 (six studies reported 0 events in both harms)</t>
   </si>
   <si>
@@ -821,6 +794,33 @@
   </si>
   <si>
     <t>N=2 n=102; Random-effects: 42.4% vs. 8.7%, OR=7.78, 95%CI: 2.83, 21.4; Fixed-effecs: OR=7.78, 95%CI: 2.83, 21.4</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 23% vs. 19.5%, OR=1.23, 95%CI: 0.94, 1.61; 95%PI: 0.88, 1.72; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 9.8% vs. 6.1%, OR=1.57, 95%CI: 1.02, 2.42, 95%PI: 0.89, 2.76; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47 (one study reported 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74, 95%PI: 0.94, 4.51; Fixed-effecs: OR=2.17, 95%CI: 1.2, 3.91 (one study reported 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=3 n=490; Random-effects: 3.3% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.44, 95%CI: 0.14, 15.03 (one study had 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=4 n=529; Random-effects: 6.2% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=3.14, 95%CI: 0.33, 29.62  (two studies had 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 5.6% vs. 3.7%, OR=1.24, 95%CI: 0.73, 2.11, 95%PI: 0.64, 2.41; Fixed-effecs: OR=1.32, 95%CI: 0.79, 2.21</t>
+  </si>
+  <si>
+    <t>N=5 n=1385; Random-effects: 5.5% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.22, 95%CI: 0.73, 2.04</t>
+  </si>
+  <si>
+    <t>N=5 n=774; Random-effects: 5.5% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.24, 95%CI: 0.48, 3.18 (one study had 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 9.3% vs. 5.2%, OR=1.76, 95%CI: 1.01, 3.08, 95%PI: 0.60, 5.23; Fixed-effecs: OR=2.01, 95%CI: 1.29, 3.14</t>
   </si>
 </sst>
 </file>
@@ -1552,13 +1552,13 @@
         <v>69</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
@@ -1575,7 +1575,7 @@
         <v>56</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>5</v>
@@ -2323,7 +2323,7 @@
         <v>80</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>4</v>
@@ -2369,7 +2369,7 @@
         <v>80</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>166</v>
+        <v>247</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>4</v>
@@ -2392,7 +2392,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>52</v>
@@ -2407,7 +2407,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="113" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>151</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>80</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>4</v>
@@ -2461,7 +2461,7 @@
         <v>80</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>4</v>
@@ -2507,7 +2507,7 @@
         <v>80</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>4</v>
@@ -2524,13 +2524,13 @@
     </row>
     <row r="12" spans="1:7" ht="104" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>51</v>
@@ -2547,16 +2547,16 @@
     </row>
     <row r="13" spans="1:7" ht="104" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>49</v>
@@ -2570,7 +2570,7 @@
     </row>
     <row r="14" spans="1:7" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>9</v>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="15" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>62</v>
@@ -2616,13 +2616,13 @@
     </row>
     <row r="16" spans="1:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>81</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>162</v>
+        <v>250</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>4</v>
@@ -2631,7 +2631,7 @@
         <v>67</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>50</v>
@@ -2639,13 +2639,13 @@
     </row>
     <row r="17" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>15</v>
@@ -2662,13 +2662,13 @@
     </row>
     <row r="18" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>4</v>
@@ -2685,13 +2685,13 @@
     </row>
     <row r="19" spans="1:7" ht="139" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>64</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="20" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
@@ -2731,7 +2731,7 @@
     </row>
     <row r="21" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>14</v>
@@ -2754,13 +2754,13 @@
     </row>
     <row r="22" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>4</v>
@@ -2777,7 +2777,7 @@
     </row>
     <row r="23" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="24" spans="1:7" ht="84" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>14</v>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="25" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="26" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>7</v>
@@ -2869,13 +2869,13 @@
     </row>
     <row r="27" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>4</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="28" spans="1:7" ht="98" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>14</v>
@@ -2915,13 +2915,13 @@
     </row>
     <row r="29" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>4</v>
@@ -2930,7 +2930,7 @@
         <v>49</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>50</v>
@@ -2938,13 +2938,13 @@
     </row>
     <row r="30" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>183</v>
+        <v>252</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>4</v>
@@ -2953,7 +2953,7 @@
         <v>49</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>50</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="31" spans="1:7" ht="85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>14</v>
@@ -2984,13 +2984,13 @@
     </row>
     <row r="32" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>4</v>
@@ -2999,7 +2999,7 @@
         <v>49</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>50</v>
@@ -3007,13 +3007,13 @@
     </row>
     <row r="33" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>15</v>
@@ -3030,13 +3030,13 @@
     </row>
     <row r="34" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>190</v>
+        <v>253</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>4</v>
@@ -3045,7 +3045,7 @@
         <v>67</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>50</v>
@@ -3053,13 +3053,13 @@
     </row>
     <row r="35" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>4</v>
@@ -3076,13 +3076,13 @@
     </row>
     <row r="36" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>4</v>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="2" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>74</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="3" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>51</v>
@@ -3187,7 +3187,7 @@
     </row>
     <row r="4" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>74</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="5" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>74</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="6" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>74</v>
@@ -3256,13 +3256,13 @@
     </row>
     <row r="7" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>51</v>
@@ -3279,7 +3279,7 @@
     </row>
     <row r="8" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>74</v>
@@ -3302,7 +3302,7 @@
     </row>
     <row r="9" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>74</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="10" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>74</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="11" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>74</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="12" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>74</v>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="13" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>74</v>
@@ -3461,7 +3461,7 @@
     </row>
     <row r="2" spans="1:7" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>14</v>
@@ -3484,7 +3484,7 @@
     </row>
     <row r="3" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>7</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="4" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>71</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="5" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>14</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="6" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="7" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>51</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="8" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>87</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="9" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>51</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="10" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>51</v>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="11" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>14</v>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="12" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>7</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="13" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>51</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="14" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>86</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="15" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>7</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="16" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>51</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="17" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>51</v>
@@ -3829,7 +3829,7 @@
     </row>
     <row r="18" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>71</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="19" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>86</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="20" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>51</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="21" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>86</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="22" spans="1:7" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>51</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="23" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>51</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="24" spans="1:7" customFormat="1" ht="139" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>14</v>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="25" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
@@ -4013,13 +4013,13 @@
     </row>
     <row r="26" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>51</v>
@@ -4036,7 +4036,7 @@
     </row>
     <row r="27" spans="1:7" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>71</v>
@@ -4059,13 +4059,13 @@
     </row>
     <row r="28" spans="1:7" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>51</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="29" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>51</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="30" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>14</v>
@@ -4128,7 +4128,7 @@
     </row>
     <row r="31" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>7</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="32" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>71</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="33" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>51</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="34" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>14</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="35" spans="1:7" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>7</v>
@@ -4243,13 +4243,13 @@
     </row>
     <row r="36" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>51</v>
@@ -4266,13 +4266,13 @@
     </row>
     <row r="37" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>86</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="38" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>71</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="39" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>7</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="40" spans="1:7" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>71</v>
@@ -4358,13 +4358,13 @@
     </row>
     <row r="41" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>51</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="42" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>71</v>

--- a/data_u1/soe_tables_2025.08.15.xlsx
+++ b/data_u1/soe_tables_2025.08.15.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F09FFE-FF05-4F4E-9CFF-7B34E80698C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B1CC9A-80B3-E945-8AE3-3127E6F8780E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21720" yWindow="-21100" windowWidth="38400" windowHeight="19840" activeTab="6" xr2:uid="{5B3852FF-2BEC-B94D-907F-9BD79E8D9C2A}"/>
   </bookViews>
@@ -544,9 +544,6 @@
     <t>Nausea/vomitting (6.1.18)</t>
   </si>
   <si>
-    <t>N=7 n=1451; Random-effects: 49.7% vs. 46.5%, OR=1.14, 95%CI: 0.81, 1.61, 95%PI: 0.50, 2.59; Fixed-effecs: OR=1.22, 95%CI: 0.98, 1.52</t>
-  </si>
-  <si>
     <t>QTc prolongation (any cut-off) (6.1.19)</t>
   </si>
   <si>
@@ -610,9 +607,6 @@
     <t>Low risk: 60% studies and 91.3% participants with schizophrenia.</t>
   </si>
   <si>
-    <t>N=4 n=524; Random-effects: 7.6% vs. 6.7%, OR=1.13, 95%CI: 0.27, 4.66, 95%PI: 0.21, 6.29; Fixed-effecs: OR=0.81, 95%CI: 0.38, 1.69</t>
-  </si>
-  <si>
     <t>Worsening of psychosis (6.1.32)</t>
   </si>
   <si>
@@ -796,31 +790,37 @@
     <t>N=2 n=102; Random-effects: 42.4% vs. 8.7%, OR=7.78, 95%CI: 2.83, 21.4; Fixed-effecs: OR=7.78, 95%CI: 2.83, 21.4</t>
   </si>
   <si>
-    <t>N=7 n=1451; Random-effects: 23% vs. 19.5%, OR=1.23, 95%CI: 0.94, 1.61; 95%PI: 0.88, 1.72; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
-  </si>
-  <si>
-    <t>N=7 n=1451; Random-effects: 9.8% vs. 6.1%, OR=1.57, 95%CI: 1.02, 2.42, 95%PI: 0.89, 2.76; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47 (one study reported 0 events in both arms)</t>
-  </si>
-  <si>
-    <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74, 95%PI: 0.94, 4.51; Fixed-effecs: OR=2.17, 95%CI: 1.2, 3.91 (one study reported 0 events in both arms)</t>
-  </si>
-  <si>
     <t>N=3 n=490; Random-effects: 3.3% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.44, 95%CI: 0.14, 15.03 (one study had 0 events in both arms)</t>
   </si>
   <si>
     <t>N=4 n=529; Random-effects: 6.2% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=3.14, 95%CI: 0.33, 29.62  (two studies had 0 events in both arms)</t>
   </si>
   <si>
-    <t>N=7 n=1451; Random-effects: 5.6% vs. 3.7%, OR=1.24, 95%CI: 0.73, 2.11, 95%PI: 0.64, 2.41; Fixed-effecs: OR=1.32, 95%CI: 0.79, 2.21</t>
-  </si>
-  <si>
     <t>N=5 n=1385; Random-effects: 5.5% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.22, 95%CI: 0.73, 2.04</t>
   </si>
   <si>
     <t>N=5 n=774; Random-effects: 5.5% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.24, 95%CI: 0.48, 3.18 (one study had 0 events in both arms)</t>
   </si>
   <si>
-    <t>N=7 n=1451; Random-effects: 9.3% vs. 5.2%, OR=1.76, 95%CI: 1.01, 3.08, 95%PI: 0.60, 5.23; Fixed-effecs: OR=2.01, 95%CI: 1.29, 3.14</t>
+    <t>N=7 n=1451; Random-effects:23% vs. 19.5%, OR=1.23, 95%CI: 1, 1.52; 95%PI: 0.88, 1.72; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects:  9.8% vs. 6.1%, OR=1.57, 95%CI: 0.94, 2.61, 95%PI: 0.89, 2.76; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47 (one study reported 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.08, 3.91, 95%PI: 0.94, 4.51; Fixed-effecs: OR=2.17, 95%CI: 1.2, 3.91 (one study reported 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 5.6% vs. 3.7%, OR=1.24, 95%CI: 0.61, 2.53, 95%PI: 0.64, 2.41; Fixed-effecs: OR=1.32, 95%CI: 0.79, 2.21</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects:  49.7% vs. 46.5%, OR=1.14, 95%CI: 0.73, 1.78, 1.61, 95%PI: 0.50, 2.59; Fixed-effecs: OR=1.22, 95%CI: 0.98, 1.52</t>
+  </si>
+  <si>
+    <t>N=4 n=524; Random-effects: 8.5% vs. 6.5%, OR=1.16, 95%CI: 0.47, 2.84, 95%PI: 0.21, 6.29; Fixed-effecs: OR=0.81, 95%CI: 0.38, 1.69</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 9.3% vs. 5.2%, OR=1.76, 95%CI: 0.92, 3.37, 95%PI: 0.60, 5.23; Fixed-effecs: OR=2.01, 95%CI: 1.29, 3.14</t>
   </si>
 </sst>
 </file>
@@ -1552,13 +1552,13 @@
         <v>69</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
@@ -1575,7 +1575,7 @@
         <v>56</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>5</v>
@@ -2323,7 +2323,7 @@
         <v>80</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>4</v>
@@ -2369,7 +2369,7 @@
         <v>80</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>4</v>
@@ -2392,7 +2392,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>52</v>
@@ -2415,7 +2415,7 @@
         <v>80</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>4</v>
@@ -2461,7 +2461,7 @@
         <v>80</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>4</v>
@@ -2499,7 +2499,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>154</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>80</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>162</v>
+        <v>252</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>4</v>
@@ -2530,7 +2530,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>51</v>
@@ -2553,7 +2553,7 @@
         <v>81</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>155</v>
@@ -2622,7 +2622,7 @@
         <v>81</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>4</v>
@@ -2645,7 +2645,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>15</v>
@@ -2685,13 +2685,13 @@
     </row>
     <row r="19" spans="1:7" ht="139" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>64</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="20" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
@@ -2731,7 +2731,7 @@
     </row>
     <row r="21" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>14</v>
@@ -2754,13 +2754,13 @@
     </row>
     <row r="22" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>4</v>
@@ -2777,7 +2777,7 @@
     </row>
     <row r="23" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="24" spans="1:7" ht="84" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>14</v>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="25" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="26" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>7</v>
@@ -2869,13 +2869,13 @@
     </row>
     <row r="27" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>4</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="28" spans="1:7" ht="98" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>14</v>
@@ -2915,13 +2915,13 @@
     </row>
     <row r="29" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>4</v>
@@ -2930,7 +2930,7 @@
         <v>49</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>50</v>
@@ -2938,13 +2938,13 @@
     </row>
     <row r="30" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>4</v>
@@ -2953,7 +2953,7 @@
         <v>49</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>50</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="31" spans="1:7" ht="85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>14</v>
@@ -2984,13 +2984,13 @@
     </row>
     <row r="32" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>4</v>
@@ -2999,7 +2999,7 @@
         <v>49</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>50</v>
@@ -3007,13 +3007,13 @@
     </row>
     <row r="33" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>15</v>
@@ -3030,13 +3030,13 @@
     </row>
     <row r="34" spans="1:7" ht="99" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>4</v>
@@ -3045,7 +3045,7 @@
         <v>67</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>50</v>
@@ -3053,13 +3053,13 @@
     </row>
     <row r="35" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>4</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="36" spans="1:7" ht="85" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>80</v>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="2" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>74</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="3" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>51</v>
@@ -3187,7 +3187,7 @@
     </row>
     <row r="4" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>74</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="5" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>74</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="6" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>74</v>
@@ -3256,13 +3256,13 @@
     </row>
     <row r="7" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>51</v>
@@ -3279,7 +3279,7 @@
     </row>
     <row r="8" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>74</v>
@@ -3302,7 +3302,7 @@
     </row>
     <row r="9" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>74</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="10" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>74</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="11" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>74</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="12" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>74</v>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="13" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>74</v>
@@ -3461,7 +3461,7 @@
     </row>
     <row r="2" spans="1:7" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>14</v>
@@ -3484,7 +3484,7 @@
     </row>
     <row r="3" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>7</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="4" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>71</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="5" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>14</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="6" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="7" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>51</v>
@@ -3599,13 +3599,13 @@
     </row>
     <row r="8" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>87</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="9" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>51</v>
@@ -3645,13 +3645,13 @@
     </row>
     <row r="10" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>51</v>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="11" spans="1:7" ht="127" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>14</v>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="12" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>7</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="13" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>51</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="14" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>86</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="15" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>7</v>
@@ -3783,13 +3783,13 @@
     </row>
     <row r="16" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>51</v>
@@ -3806,13 +3806,13 @@
     </row>
     <row r="17" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>51</v>
@@ -3829,7 +3829,7 @@
     </row>
     <row r="18" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>71</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="19" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>86</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="20" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>51</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="21" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>86</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="22" spans="1:7" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>51</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="23" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>51</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="24" spans="1:7" customFormat="1" ht="139" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>14</v>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="25" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
@@ -4013,13 +4013,13 @@
     </row>
     <row r="26" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>51</v>
@@ -4036,7 +4036,7 @@
     </row>
     <row r="27" spans="1:7" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>71</v>
@@ -4059,13 +4059,13 @@
     </row>
     <row r="28" spans="1:7" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>51</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="29" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>51</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="30" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>14</v>
@@ -4128,7 +4128,7 @@
     </row>
     <row r="31" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>7</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="32" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>71</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="33" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>51</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="34" spans="1:7" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>14</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="35" spans="1:7" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>7</v>
@@ -4243,13 +4243,13 @@
     </row>
     <row r="36" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>51</v>
@@ -4266,13 +4266,13 @@
     </row>
     <row r="37" spans="1:7" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>86</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="38" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>71</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="39" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>7</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="40" spans="1:7" ht="46" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>71</v>
@@ -4358,13 +4358,13 @@
     </row>
     <row r="41" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>51</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="42" spans="1:7" ht="43" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>71</v>

--- a/data_u1/soe_tables_2025.08.15.xlsx
+++ b/data_u1/soe_tables_2025.08.15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B1CC9A-80B3-E945-8AE3-3127E6F8780E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6018EB-FF8B-9D43-8D20-F5355E5B365A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-21100" windowWidth="38400" windowHeight="19840" activeTab="6" xr2:uid="{5B3852FF-2BEC-B94D-907F-9BD79E8D9C2A}"/>
+    <workbookView xWindow="-21720" yWindow="-20840" windowWidth="38400" windowHeight="19840" activeTab="8" xr2:uid="{5B3852FF-2BEC-B94D-907F-9BD79E8D9C2A}"/>
   </bookViews>
   <sheets>
     <sheet name="sch_ac_ta1_pl_eff" sheetId="1" r:id="rId1"/>
@@ -790,37 +790,37 @@
     <t>N=2 n=102; Random-effects: 42.4% vs. 8.7%, OR=7.78, 95%CI: 2.83, 21.4; Fixed-effecs: OR=7.78, 95%CI: 2.83, 21.4</t>
   </si>
   <si>
-    <t>N=3 n=490; Random-effects: 3.3% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.44, 95%CI: 0.14, 15.03 (one study had 0 events in both arms)</t>
-  </si>
-  <si>
-    <t>N=4 n=529; Random-effects: 6.2% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=3.14, 95%CI: 0.33, 29.62  (two studies had 0 events in both arms)</t>
-  </si>
-  <si>
     <t>N=5 n=1385; Random-effects: 5.5% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.22, 95%CI: 0.73, 2.04</t>
   </si>
   <si>
-    <t>N=5 n=774; Random-effects: 5.5% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.24, 95%CI: 0.48, 3.18 (one study had 0 events in both arms)</t>
-  </si>
-  <si>
     <t>N=7 n=1451; Random-effects:23% vs. 19.5%, OR=1.23, 95%CI: 1, 1.52; 95%PI: 0.88, 1.72; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
   </si>
   <si>
-    <t>N=7 n=1451; Random-effects:  9.8% vs. 6.1%, OR=1.57, 95%CI: 0.94, 2.61, 95%PI: 0.89, 2.76; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47 (one study reported 0 events in both arms)</t>
-  </si>
-  <si>
-    <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.08, 3.91, 95%PI: 0.94, 4.51; Fixed-effecs: OR=2.17, 95%CI: 1.2, 3.91 (one study reported 0 events in both arms)</t>
-  </si>
-  <si>
     <t>N=7 n=1451; Random-effects: 5.6% vs. 3.7%, OR=1.24, 95%CI: 0.61, 2.53, 95%PI: 0.64, 2.41; Fixed-effecs: OR=1.32, 95%CI: 0.79, 2.21</t>
   </si>
   <si>
     <t>N=7 n=1451; Random-effects:  49.7% vs. 46.5%, OR=1.14, 95%CI: 0.73, 1.78, 1.61, 95%PI: 0.50, 2.59; Fixed-effecs: OR=1.22, 95%CI: 0.98, 1.52</t>
   </si>
   <si>
-    <t>N=4 n=524; Random-effects: 8.5% vs. 6.5%, OR=1.16, 95%CI: 0.47, 2.84, 95%PI: 0.21, 6.29; Fixed-effecs: OR=0.81, 95%CI: 0.38, 1.69</t>
-  </si>
-  <si>
-    <t>N=7 n=1451; Random-effects: 9.3% vs. 5.2%, OR=1.76, 95%CI: 0.92, 3.37, 95%PI: 0.60, 5.23; Fixed-effecs: OR=2.01, 95%CI: 1.29, 3.14</t>
+    <t>N=7 n=1451; Random-effects:  9.3% vs. 6.1%, OR=1.57, 95%CI: 0.94, 2.61, 95%PI: 0.89, 2.76; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47 (one study reported 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 5.6% vs. 2.8%, OR=2.05, 95%CI: 1.08, 3.91, 95%PI: 0.94, 4.51; Fixed-effecs: OR=2.17, 95%CI: 1.2, 3.91 (one study reported 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=3 n=490; Random-effects: 0.5% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.44, 95%CI: 0.14, 15.03 (one study had 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=4 n=529; Random-effects: 0.8% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=3.14, 95%CI: 0.33, 29.62  (two studies had 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=5 n=774; Random-effects:  1.6% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.24, 95%CI: 0.48, 3.18 (one study had 0 events in both arms)</t>
+  </si>
+  <si>
+    <t>N=7 n=1451; Random-effects: 8.8% vs. 5.2%, OR=1.76, 95%CI: 0.92, 3.37, 95%PI: 0.60, 5.23; Fixed-effecs: OR=2.01, 95%CI: 1.29, 3.14</t>
+  </si>
+  <si>
+    <t>N=4 n=524; Random-effects: 7.4% vs. 6.5%, OR=1.16, 95%CI: 0.47, 2.84, 95%PI: 0.21, 6.29; Fixed-effecs: OR=0.81, 95%CI: 0.38, 1.69</t>
   </si>
 </sst>
 </file>
@@ -2323,7 +2323,7 @@
         <v>80</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>4</v>
@@ -2369,7 +2369,7 @@
         <v>80</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>4</v>
@@ -2415,7 +2415,7 @@
         <v>80</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>4</v>
@@ -2507,7 +2507,7 @@
         <v>80</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>4</v>
@@ -2553,7 +2553,7 @@
         <v>81</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>155</v>
@@ -2622,7 +2622,7 @@
         <v>81</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>4</v>
@@ -2668,7 +2668,7 @@
         <v>80</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>4</v>
@@ -2944,7 +2944,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>4</v>
@@ -3036,7 +3036,7 @@
         <v>80</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>4</v>
@@ -3059,7 +3059,7 @@
         <v>80</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>4</v>
@@ -3082,7 +3082,7 @@
         <v>80</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>4</v>
